--- a/public/exports/29188955.xlsx
+++ b/public/exports/29188955.xlsx
@@ -81,16 +81,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5489077</t>
+          <t xml:space="preserve">301970, 301971</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F2">
-        <v>296</v>
+        <v>2083</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -131,16 +131,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5489577</t>
+          <t xml:space="preserve">302908, 302909</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F3">
-        <v>541</v>
+        <v>4625</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -181,16 +181,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5490002</t>
+          <t xml:space="preserve">302956</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F4">
-        <v>1788</v>
+        <v>387</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5490201</t>
+          <t xml:space="preserve">302956</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F5">
-        <v>287</v>
+        <v>1011</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">734121, 5489406</t>
+          <t xml:space="preserve">5489077</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F6">
-        <v>1063</v>
+        <v>296</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">734136, 5490237</t>
+          <t xml:space="preserve">5489577</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F7">
-        <v>593</v>
+        <v>541</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">734155, 8866627</t>
+          <t xml:space="preserve">5490002</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F8">
-        <v>442</v>
+        <v>1788</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">734155, 8866627</t>
+          <t xml:space="preserve">5490201</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F9">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">734158, 3074235</t>
+          <t xml:space="preserve">734121, 5489406</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F10">
-        <v>1650</v>
+        <v>1063</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">734202, 8866627</t>
+          <t xml:space="preserve">734136, 5490237</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F11">
-        <v>387</v>
+        <v>593</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9547826</t>
+          <t xml:space="preserve">734158, 3074235</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F12">
-        <v>366</v>
+        <v>1650</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,35 +631,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5489077</t>
+          <t xml:space="preserve">9547826</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F13">
-        <v>560</v>
+        <v>366</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">311425472</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-02</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3068632</t>
+          <t xml:space="preserve">5489077</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="F14">
-        <v>1101</v>
+        <v>560</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482524</t>
+          <t xml:space="preserve">311425472</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-14</t>
+          <t xml:space="preserve">2030-03-02</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -731,20 +731,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3077138</t>
+          <t xml:space="preserve">3068632</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F15">
-        <v>265</v>
+        <v>1101</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482534</t>
+          <t xml:space="preserve">311482524</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -781,25 +781,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3075730</t>
+          <t xml:space="preserve">3077138</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F16">
-        <v>969</v>
+        <v>265</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311492855</t>
+          <t xml:space="preserve">311482534</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-04</t>
+          <t xml:space="preserve">2030-12-14</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8644450</t>
+          <t xml:space="preserve">3075730</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -840,11 +840,11 @@
         </is>
       </c>
       <c r="F17">
-        <v>701</v>
+        <v>969</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311492859</t>
+          <t xml:space="preserve">311492855</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -886,20 +886,20 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F18">
-        <v>2989</v>
+        <v>701</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493489</t>
+          <t xml:space="preserve">311492859</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-07</t>
+          <t xml:space="preserve">2031-02-04</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -931,25 +931,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5490955</t>
+          <t xml:space="preserve">8644450</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F19">
-        <v>623</v>
+        <v>2989</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529196</t>
+          <t xml:space="preserve">311493489</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-19</t>
+          <t xml:space="preserve">2031-02-07</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -986,11 +986,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F20">
-        <v>373</v>
+        <v>623</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1036,20 +1036,20 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F21">
-        <v>340</v>
+        <v>373</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529186</t>
+          <t xml:space="preserve">311529196</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-22</t>
+          <t xml:space="preserve">2031-02-19</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1081,25 +1081,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5489721</t>
+          <t xml:space="preserve">5490955</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F22">
-        <v>828</v>
+        <v>340</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529152</t>
+          <t xml:space="preserve">311529186</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-07</t>
+          <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1136,20 +1136,20 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F23">
-        <v>5101</v>
+        <v>828</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529147</t>
+          <t xml:space="preserve">311529152</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-05-07</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">302908, 302909</t>
+          <t xml:space="preserve">5489721</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="F24">
-        <v>4625</v>
+        <v>5101</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542244</t>
+          <t xml:space="preserve">311529147</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-20</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">301970, 301971</t>
+          <t xml:space="preserve">5489428</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1590,11 +1590,11 @@
         </is>
       </c>
       <c r="F32">
-        <v>2083</v>
+        <v>866</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568316</t>
+          <t xml:space="preserve">311568384</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5489428</t>
+          <t xml:space="preserve">7099542</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="F33">
-        <v>866</v>
+        <v>988</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568384</t>
+          <t xml:space="preserve">311571524</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-16</t>
+          <t xml:space="preserve">2032-01-10</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1686,15 +1686,15 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F34">
-        <v>988</v>
+        <v>886</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571524</t>
+          <t xml:space="preserve">311571525</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1731,25 +1731,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">7099542</t>
+          <t xml:space="preserve">3074196</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F35">
-        <v>886</v>
+        <v>2602</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571525</t>
+          <t xml:space="preserve">311580361</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-10</t>
+          <t xml:space="preserve">2032-02-22</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1786,11 +1786,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F36">
-        <v>2602</v>
+        <v>352</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1836,11 +1836,11 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F37">
-        <v>352</v>
+        <v>586</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1886,15 +1886,15 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F38">
-        <v>586</v>
+        <v>395</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311580361</t>
+          <t xml:space="preserve">311580360</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3074196</t>
+          <t xml:space="preserve">5488951</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F39">
-        <v>395</v>
+        <v>668</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311580360</t>
+          <t xml:space="preserve">311584100</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-22</t>
+          <t xml:space="preserve">2032-03-10</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5488951</t>
+          <t xml:space="preserve">5490140</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1990,16 +1990,16 @@
         </is>
       </c>
       <c r="F40">
-        <v>668</v>
+        <v>852</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584100</t>
+          <t xml:space="preserve">311585659</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-10</t>
+          <t xml:space="preserve">2032-03-16</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5490140</t>
+          <t xml:space="preserve">734155, 8866627</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F41">
-        <v>852</v>
+        <v>442</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585659</t>
+          <t xml:space="preserve">311585991</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-16</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2081,25 +2081,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3068632</t>
+          <t xml:space="preserve">734155, 8866627</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="F42">
-        <v>393</v>
+        <v>264</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586376</t>
+          <t xml:space="preserve">311585991</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2131,25 +2131,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5490100</t>
+          <t xml:space="preserve">734202, 8866627</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F43">
-        <v>2067</v>
+        <v>387</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586784</t>
+          <t xml:space="preserve">311585991</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-21</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5490887</t>
+          <t xml:space="preserve">3068632</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F44">
-        <v>1786</v>
+        <v>393</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587824</t>
+          <t xml:space="preserve">311586376</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-24</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9547828</t>
+          <t xml:space="preserve">5490100</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="F45">
-        <v>305</v>
+        <v>2067</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588491</t>
+          <t xml:space="preserve">311586784</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-03-21</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2281,25 +2281,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">302956</t>
+          <t xml:space="preserve">5490887</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F46">
-        <v>387</v>
+        <v>1786</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311589021</t>
+          <t xml:space="preserve">311587824</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">302956</t>
+          <t xml:space="preserve">9547828</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F47">
-        <v>1011</v>
+        <v>305</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311589021</t>
+          <t xml:space="preserve">311588491</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-29</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">

--- a/public/exports/29188955.xlsx
+++ b/public/exports/29188955.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:L50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 55</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5932</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">301970, 301971</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>2083</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tullebølle Centret 2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5953</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">302908, 302909</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>4625</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spodsbjergvej 201</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">302956</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>387</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spodsbjergvej 201</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">302956</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>1011</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østergade 25</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">5489077</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>296</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østerport 7</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">5489577</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>541</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engdraget 10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">5490002</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>1788</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandbakken 17</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">5490201</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>287</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnepladsen 39</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">734121, 5489406</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>1063</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rue Mark 9</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">734136, 5490237</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>593</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hallinggade 25B</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5932</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">734158, 3074235</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>1650</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engdraget 8</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">9547826</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>366</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østergade 23</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">5489077</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>560</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">311425472</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-03-02</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vindeltorpvej 1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">3068632</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>1101</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">311482524</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-12-14</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stationsvej 6</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5935</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">3077138</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>265</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">311482534</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-12-14</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langegade 30B</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">3075730</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>969</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">311492855</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-04</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langegade 30A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">8644450</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>701</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">311492859</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-04</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langegade 30A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">8644450</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>2989</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">311493489</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-07</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ahlefeldtsgade 13</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">5490955</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>623</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">311529196</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-19</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ahlefeldtsgade 13</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">5490955</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>373</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">311529196</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-19</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ahlefeldtsgade 13</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">5490955</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>340</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">311529186</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fredensvej 1A</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">5489721</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>828</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">311529152</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-07</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fredensvej 1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">5489721</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>5101</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311529147</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tværvej 15</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5932</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">3074374</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>308</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311542539</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-08-23</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stigtehaven 6</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5953</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">9369230</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>1499</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">311545477</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fredensvej 1B</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">5489721</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>347</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311549943</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-22</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hinestien 1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">7099564</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>354</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311563855</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørrebro 75</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">100040956</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>316</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311551653</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-29</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnegade 118</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">100062527</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>897</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311563862</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-09</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnegade 118</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">100062527</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>3054</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311563858</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-11-11</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnegade 7</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">5489428</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>866</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311568384</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jens Winthers Vej 12</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">7099542</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>988</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311571524</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-01-10</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jens Winthers Vej 12</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">7099542</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>886</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311571525</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-01-10</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 64</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5932</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">3074196</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>2602</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311580361</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-02-22</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 64</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5932</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">3074196</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>352</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311580361</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-02-22</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 64</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5932</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">3074196</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>586</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311580361</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-02-22</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 64</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5932</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">3074196</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>395</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311580360</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-02-22</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ørstedsgade 16</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">5488951</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>668</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311584100</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-10</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mjølbyvej 8</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">5490140</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>852</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311585659</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-16</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnegade 2A</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5935</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">734155, 8866627</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">23</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>442</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311585991</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnegade 6A</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5935</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">734155, 8866627</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">42</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>264</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311585991</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Værftsvej 59</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5935</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">734202, 8866627</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">37</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>387</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311585991</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vindeltorpvej 1A</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">3068632</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>393</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311586376</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spodsbjergvej 129</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">5490100</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>2067</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311586784</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-21</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnegade 118B</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">5490887</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>1786</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311587824</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Spodsbjergvej 52B</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">9547828</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>305</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311588491</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordre Landevej 65</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">3068305</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>254</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311592796</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordre Landevej 65</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5900</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">3068305</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>548</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311592796</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,39 +2971,49 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Snødevej 138</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5953</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">3069065</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>1663</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311592782</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J50"/>
+  <autoFilter ref="A1:L50"/>
 </worksheet>
 </file>
--- a/public/exports/29188955.xlsx
+++ b/public/exports/29188955.xlsx
@@ -91,17 +91,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 55</t>
+          <t xml:space="preserve">Engdraget 10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5932</t>
+          <t xml:space="preserve">5900</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301970, 301971</t>
+          <t xml:space="preserve">5490002</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -110,7 +110,7 @@
         </is>
       </c>
       <c r="H2">
-        <v>2083</v>
+        <v>1788</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,26 +151,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tullebølle Centret 2</t>
+          <t xml:space="preserve">Engdraget 8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5953</t>
+          <t xml:space="preserve">5900</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302908, 302909</t>
+          <t xml:space="preserve">9547826</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H3">
-        <v>4625</v>
+        <v>366</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spodsbjergvej 201</t>
+          <t xml:space="preserve">Hallinggade 25B</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">5932</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">302956</t>
+          <t xml:space="preserve">734158, 3074235</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H4">
-        <v>387</v>
+        <v>1650</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spodsbjergvej 201</t>
+          <t xml:space="preserve">Havnepladsen 39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">302956</t>
+          <t xml:space="preserve">734121, 5489406</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H5">
-        <v>1011</v>
+        <v>1063</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 25</t>
+          <t xml:space="preserve">Rue Mark 9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5489077</t>
+          <t xml:space="preserve">734136, 5490237</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H6">
-        <v>296</v>
+        <v>593</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østerport 7</t>
+          <t xml:space="preserve">Strandbakken 17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5489577</t>
+          <t xml:space="preserve">5490201</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H7">
-        <v>541</v>
+        <v>287</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 10</t>
+          <t xml:space="preserve">Østergade 25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,16 +461,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5490002</t>
+          <t xml:space="preserve">5489077</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H8">
-        <v>1788</v>
+        <v>296</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandbakken 17</t>
+          <t xml:space="preserve">Østerport 7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,16 +521,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5490201</t>
+          <t xml:space="preserve">5489577</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H9">
-        <v>287</v>
+        <v>541</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnepladsen 39</t>
+          <t xml:space="preserve">Østergade 23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,35 +581,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">734121, 5489406</t>
+          <t xml:space="preserve">5489077</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H10">
-        <v>1063</v>
+        <v>560</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311425472</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2030-03-02</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -631,45 +631,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rue Mark 9</t>
+          <t xml:space="preserve">Stationsvej 6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">5935</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">734136, 5490237</t>
+          <t xml:space="preserve">3077138</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H11">
-        <v>593</v>
+        <v>265</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311482534</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2030-12-14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -691,45 +691,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hallinggade 25B</t>
+          <t xml:space="preserve">Vindeltorpvej 1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5932</t>
+          <t xml:space="preserve">5900</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">734158, 3074235</t>
+          <t xml:space="preserve">3068632</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H12">
-        <v>1650</v>
+        <v>1101</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311482524</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2030-12-14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 8</t>
+          <t xml:space="preserve">Langegade 30A</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,35 +761,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">9547826</t>
+          <t xml:space="preserve">8644450</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H13">
-        <v>366</v>
+        <v>701</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311492859</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2031-02-04</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 23</t>
+          <t xml:space="preserve">Langegade 30B</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5489077</t>
+          <t xml:space="preserve">3075730</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -830,16 +830,16 @@
         </is>
       </c>
       <c r="H14">
-        <v>560</v>
+        <v>969</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">311425472</t>
+          <t xml:space="preserve">311492855</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-02</t>
+          <t xml:space="preserve">2031-02-04</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeltorpvej 1</t>
+          <t xml:space="preserve">Langegade 30A</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,25 +881,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3068632</t>
+          <t xml:space="preserve">8644450</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H15">
-        <v>1101</v>
+        <v>2989</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482524</t>
+          <t xml:space="preserve">311493489</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-14</t>
+          <t xml:space="preserve">2031-02-07</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -931,35 +931,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 6</t>
+          <t xml:space="preserve">Ahlefeldtsgade 13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5935</t>
+          <t xml:space="preserve">5900</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3077138</t>
+          <t xml:space="preserve">5490955</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H16">
-        <v>265</v>
+        <v>623</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482534</t>
+          <t xml:space="preserve">311529196</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-14</t>
+          <t xml:space="preserve">2031-02-19</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langegade 30B</t>
+          <t xml:space="preserve">Ahlefeldtsgade 13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,25 +1001,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3075730</t>
+          <t xml:space="preserve">5490955</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H17">
-        <v>969</v>
+        <v>373</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311492855</t>
+          <t xml:space="preserve">311529196</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-04</t>
+          <t xml:space="preserve">2031-02-19</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langegade 30A</t>
+          <t xml:space="preserve">Ahlefeldtsgade 13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,25 +1061,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">8644450</t>
+          <t xml:space="preserve">5490955</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H18">
-        <v>701</v>
+        <v>340</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311492859</t>
+          <t xml:space="preserve">311529186</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-04</t>
+          <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langegade 30A</t>
+          <t xml:space="preserve">Fredensvej 1A</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8644450</t>
+          <t xml:space="preserve">5489721</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1130,16 +1130,16 @@
         </is>
       </c>
       <c r="H19">
-        <v>2989</v>
+        <v>828</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493489</t>
+          <t xml:space="preserve">311529152</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-07</t>
+          <t xml:space="preserve">2031-05-07</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahlefeldtsgade 13</t>
+          <t xml:space="preserve">Fredensvej 1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5490955</t>
+          <t xml:space="preserve">5489721</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="H20">
-        <v>623</v>
+        <v>5101</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529196</t>
+          <t xml:space="preserve">311529147</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-19</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1231,35 +1231,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahlefeldtsgade 13</t>
+          <t xml:space="preserve">Tullebølle Centret 2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">5953</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5490955</t>
+          <t xml:space="preserve">302908, 302909</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>373</v>
+        <v>4625</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529196</t>
+          <t xml:space="preserve">311542244</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-19</t>
+          <t xml:space="preserve">2031-08-20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1291,35 +1291,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahlefeldtsgade 13</t>
+          <t xml:space="preserve">Tværvej 15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">5932</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5490955</t>
+          <t xml:space="preserve">3074374</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H22">
-        <v>340</v>
+        <v>308</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529186</t>
+          <t xml:space="preserve">311542539</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-22</t>
+          <t xml:space="preserve">2031-08-23</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1351,35 +1351,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 1A</t>
+          <t xml:space="preserve">Stigtehaven 6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">5953</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5489721</t>
+          <t xml:space="preserve">9369230</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H23">
-        <v>828</v>
+        <v>1499</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529152</t>
+          <t xml:space="preserve">311545477</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-07</t>
+          <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 1</t>
+          <t xml:space="preserve">Fredensvej 1B</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1426,20 +1426,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H24">
-        <v>5101</v>
+        <v>347</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311529147</t>
+          <t xml:space="preserve">311549943</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-09-22</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvej 15</t>
+          <t xml:space="preserve">Hinestien 1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5932</t>
+          <t xml:space="preserve">5900</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">3074374</t>
+          <t xml:space="preserve">7099564</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="H25">
-        <v>308</v>
+        <v>354</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311542539</t>
+          <t xml:space="preserve">311563855</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-23</t>
+          <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1531,17 +1531,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stigtehaven 6</t>
+          <t xml:space="preserve">Nørrebro 75</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5953</t>
+          <t xml:space="preserve">5900</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">9369230</t>
+          <t xml:space="preserve">100040956</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1550,16 +1550,16 @@
         </is>
       </c>
       <c r="H26">
-        <v>1499</v>
+        <v>316</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311545477</t>
+          <t xml:space="preserve">311551653</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-02</t>
+          <t xml:space="preserve">2031-09-29</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 1B</t>
+          <t xml:space="preserve">Havnegade 118</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1601,25 +1601,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5489721</t>
+          <t xml:space="preserve">100062527</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H27">
-        <v>347</v>
+        <v>897</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549943</t>
+          <t xml:space="preserve">311563862</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-22</t>
+          <t xml:space="preserve">2031-11-09</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hinestien 1</t>
+          <t xml:space="preserve">Havnegade 118</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">7099564</t>
+          <t xml:space="preserve">100062527</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1670,16 +1670,16 @@
         </is>
       </c>
       <c r="H28">
-        <v>354</v>
+        <v>3054</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311563855</t>
+          <t xml:space="preserve">311563858</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-27</t>
+          <t xml:space="preserve">2031-11-11</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebro 75</t>
+          <t xml:space="preserve">Havnegade 7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">100040956</t>
+          <t xml:space="preserve">5489428</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="H29">
-        <v>316</v>
+        <v>866</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551653</t>
+          <t xml:space="preserve">311568384</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-29</t>
+          <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1771,35 +1771,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 118</t>
+          <t xml:space="preserve">Hovedgaden 55</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">5932</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">100062527</t>
+          <t xml:space="preserve">301970, 301971</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H30">
-        <v>897</v>
+        <v>2083</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311563862</t>
+          <t xml:space="preserve">311568316</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-09</t>
+          <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 118</t>
+          <t xml:space="preserve">Jens Winthers Vej 12</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">100062527</t>
+          <t xml:space="preserve">7099542</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="H31">
-        <v>3054</v>
+        <v>988</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311563858</t>
+          <t xml:space="preserve">311571524</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-11</t>
+          <t xml:space="preserve">2032-01-10</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 7</t>
+          <t xml:space="preserve">Jens Winthers Vej 12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,25 +1901,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5489428</t>
+          <t xml:space="preserve">7099542</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H32">
-        <v>866</v>
+        <v>886</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568384</t>
+          <t xml:space="preserve">311571525</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-16</t>
+          <t xml:space="preserve">2032-01-10</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1951,17 +1951,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jens Winthers Vej 12</t>
+          <t xml:space="preserve">Hovedgaden 64</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">5932</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">7099542</t>
+          <t xml:space="preserve">3074196</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1970,16 +1970,16 @@
         </is>
       </c>
       <c r="H33">
-        <v>988</v>
+        <v>2602</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571524</t>
+          <t xml:space="preserve">311580361</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-10</t>
+          <t xml:space="preserve">2032-02-22</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jens Winthers Vej 12</t>
+          <t xml:space="preserve">Hovedgaden 64</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">5932</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">7099542</t>
+          <t xml:space="preserve">3074196</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2030,16 +2030,16 @@
         </is>
       </c>
       <c r="H34">
-        <v>886</v>
+        <v>352</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571525</t>
+          <t xml:space="preserve">311580361</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-10</t>
+          <t xml:space="preserve">2032-02-22</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2086,11 +2086,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H35">
-        <v>2602</v>
+        <v>586</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2146,15 +2146,15 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H36">
-        <v>352</v>
+        <v>395</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311580361</t>
+          <t xml:space="preserve">311580360</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2191,35 +2191,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 64</t>
+          <t xml:space="preserve">Ørstedsgade 16</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5932</t>
+          <t xml:space="preserve">5900</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3074196</t>
+          <t xml:space="preserve">5488951</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H37">
-        <v>586</v>
+        <v>668</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311580361</t>
+          <t xml:space="preserve">311584100</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-22</t>
+          <t xml:space="preserve">2032-03-10</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2251,35 +2251,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 64</t>
+          <t xml:space="preserve">Mjølbyvej 8</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5932</t>
+          <t xml:space="preserve">5900</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3074196</t>
+          <t xml:space="preserve">5490140</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H38">
-        <v>395</v>
+        <v>852</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311580360</t>
+          <t xml:space="preserve">311585659</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-22</t>
+          <t xml:space="preserve">2032-03-16</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2311,35 +2311,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedsgade 16</t>
+          <t xml:space="preserve">Havnegade 2A</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">5935</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5488951</t>
+          <t xml:space="preserve">734155, 8866627</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="H39">
-        <v>668</v>
+        <v>442</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584100</t>
+          <t xml:space="preserve">311585991</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-10</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2371,35 +2371,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mjølbyvej 8</t>
+          <t xml:space="preserve">Havnegade 6A</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5900</t>
+          <t xml:space="preserve">5935</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5490140</t>
+          <t xml:space="preserve">734155, 8866627</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="H40">
-        <v>852</v>
+        <v>264</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585659</t>
+          <t xml:space="preserve">311585991</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-16</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 2A</t>
+          <t xml:space="preserve">Værftsvej 59</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,16 +2441,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">734155, 8866627</t>
+          <t xml:space="preserve">734202, 8866627</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="H41">
-        <v>442</v>
+        <v>387</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 6A</t>
+          <t xml:space="preserve">Vindeltorpvej 1A</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5935</t>
+          <t xml:space="preserve">5900</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">734155, 8866627</t>
+          <t xml:space="preserve">3068632</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H42">
-        <v>264</v>
+        <v>393</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585991</t>
+          <t xml:space="preserve">311586376</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2551,35 +2551,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Værftsvej 59</t>
+          <t xml:space="preserve">Spodsbjergvej 129</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5935</t>
+          <t xml:space="preserve">5900</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">734202, 8866627</t>
+          <t xml:space="preserve">5490100</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>387</v>
+        <v>2067</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311585991</t>
+          <t xml:space="preserve">311586784</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-21</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeltorpvej 1A</t>
+          <t xml:space="preserve">Havnegade 118B</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,25 +2621,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3068632</t>
+          <t xml:space="preserve">5490887</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H44">
-        <v>393</v>
+        <v>1786</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586376</t>
+          <t xml:space="preserve">311587824</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spodsbjergvej 129</t>
+          <t xml:space="preserve">Spodsbjergvej 52B</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5490100</t>
+          <t xml:space="preserve">9547828</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2690,16 +2690,16 @@
         </is>
       </c>
       <c r="H45">
-        <v>2067</v>
+        <v>305</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586784</t>
+          <t xml:space="preserve">311588491</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-21</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 118B</t>
+          <t xml:space="preserve">Spodsbjergvej 201</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2741,25 +2741,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5490887</t>
+          <t xml:space="preserve">302956</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H46">
-        <v>1786</v>
+        <v>387</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587824</t>
+          <t xml:space="preserve">311589021</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-24</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spodsbjergvej 52B</t>
+          <t xml:space="preserve">Spodsbjergvej 201</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,25 +2801,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">9547828</t>
+          <t xml:space="preserve">302956</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H47">
-        <v>305</v>
+        <v>1011</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588491</t>
+          <t xml:space="preserve">311589021</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">

--- a/public/exports/29188955.xlsx
+++ b/public/exports/29188955.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:M50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -599,15 +644,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-02</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -659,15 +709,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-14</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -719,15 +774,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-14</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -779,15 +839,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-04</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -839,15 +904,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-04</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-07</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-19</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-19</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-22</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-07</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-20</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-23</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-02</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-22</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-27</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-29</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-09</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-11</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-10</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-10</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-22</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-22</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-22</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-22</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-10</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-16</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-21</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-29</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,21 +3244,26 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L50"/>
+  <autoFilter ref="A1:M50"/>
 </worksheet>
 </file>